--- a/smart-teaching-backend/uploads/template/用户管理批量导入模版.xlsx
+++ b/smart-teaching-backend/uploads/template/用户管理批量导入模版.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30412"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{099CAF48-EFBD-41A1-9161-DE04200BF42C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C1B23C4-04BD-47EF-9075-DCEA0F27849E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="50" windowWidth="11910" windowHeight="10060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="41">
   <si>
     <t>账号</t>
   </si>
@@ -38,97 +38,115 @@
     <t>邮箱</t>
   </si>
   <si>
-    <t>学院 ID</t>
-  </si>
-  <si>
-    <t>专业 ID</t>
-  </si>
-  <si>
-    <t>班级 ID</t>
-  </si>
-  <si>
     <t>zhangsan</t>
   </si>
   <si>
     <t>张景浩</t>
   </si>
   <si>
-    <t>e10adc3949ba59abbe56e057f20f883e</t>
+    <t>student</t>
+  </si>
+  <si>
+    <t>13812457891</t>
+  </si>
+  <si>
+    <t>zhangjinghao@stu.smart.edu.cn</t>
+  </si>
+  <si>
+    <t>lisi</t>
+  </si>
+  <si>
+    <t>李思瑶</t>
+  </si>
+  <si>
+    <t>teacher</t>
+  </si>
+  <si>
+    <t>13923564782</t>
+  </si>
+  <si>
+    <t>lisiyao@smart.edu.cn</t>
+  </si>
+  <si>
+    <t>wangwu</t>
+  </si>
+  <si>
+    <t>王梓恒</t>
+  </si>
+  <si>
+    <t>13734659873</t>
+  </si>
+  <si>
+    <t>wangziheng@stu.smart.edu.cn</t>
+  </si>
+  <si>
+    <t>zhaoliu</t>
+  </si>
+  <si>
+    <t>赵启元</t>
+  </si>
+  <si>
+    <t>13898761234</t>
+  </si>
+  <si>
+    <t>zhaoliu@smart.edu.cn</t>
+  </si>
+  <si>
+    <t>qianqi</t>
+  </si>
+  <si>
+    <t>钱若汐</t>
+  </si>
+  <si>
+    <t>15845782365</t>
+  </si>
+  <si>
+    <t>qianruoxi@stu.smart.edu.cn</t>
   </si>
   <si>
     <t>男</t>
   </si>
   <si>
-    <t>student</t>
-  </si>
-  <si>
-    <t>13812457891</t>
-  </si>
-  <si>
-    <t>zhangjinghao@stu.smart.edu.cn</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>lisi</t>
-  </si>
-  <si>
-    <t>李思瑶</t>
-  </si>
-  <si>
     <t>女</t>
   </si>
   <si>
-    <t>teacher</t>
-  </si>
-  <si>
-    <t>13923564782</t>
-  </si>
-  <si>
-    <t>lisiyao@smart.edu.cn</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>wangwu</t>
-  </si>
-  <si>
-    <t>王梓恒</t>
-  </si>
-  <si>
-    <t>13734659873</t>
-  </si>
-  <si>
-    <t>wangziheng@stu.smart.edu.cn</t>
-  </si>
-  <si>
-    <t>zhaoliu</t>
-  </si>
-  <si>
-    <t>赵启元</t>
-  </si>
-  <si>
-    <t>root</t>
-  </si>
-  <si>
-    <t>13898761234</t>
-  </si>
-  <si>
-    <t>zhaoliu@smart.edu.cn</t>
-  </si>
-  <si>
-    <t>qianqi</t>
-  </si>
-  <si>
-    <t>钱若汐</t>
-  </si>
-  <si>
-    <t>15845782365</t>
-  </si>
-  <si>
-    <t>qianruoxi@stu.smart.edu.cn</t>
+    <t>admin</t>
+  </si>
+  <si>
+    <t>学院</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>专业</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>班级</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>计算机科学与技术学院</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>软件工程</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>软工2301班</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>外国语学院</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>英语</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>英语2301班</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -513,17 +531,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J6"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="10" customWidth="1"/>
     <col min="3" max="3" width="34" customWidth="1"/>
     <col min="4" max="5" width="10" customWidth="1"/>
     <col min="6" max="6" width="13" customWidth="1"/>
     <col min="7" max="7" width="31" customWidth="1"/>
-    <col min="8" max="10" width="10" customWidth="1"/>
+    <col min="8" max="8" width="24.453125" customWidth="1"/>
+    <col min="9" max="10" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -546,177 +565,191 @@
         <v>6</v>
       </c>
       <c r="H1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="B2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="C2">
+        <v>123456</v>
+      </c>
+      <c r="D2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E2" t="s">
         <v>9</v>
       </c>
+      <c r="F2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2" t="s">
+        <v>11</v>
+      </c>
+      <c r="H2" t="s">
+        <v>35</v>
+      </c>
+      <c r="I2" t="s">
+        <v>36</v>
+      </c>
+      <c r="J2" t="s">
+        <v>37</v>
+      </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C2" t="s">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>12</v>
       </c>
-      <c r="D2" t="s">
+      <c r="B3" t="s">
         <v>13</v>
       </c>
-      <c r="E2" t="s">
+      <c r="C3">
+        <v>123456</v>
+      </c>
+      <c r="D3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E3" t="s">
         <v>14</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F3" t="s">
         <v>15</v>
       </c>
-      <c r="G2" t="s">
+      <c r="G3" t="s">
         <v>16</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I3" t="s">
+        <v>36</v>
+      </c>
+      <c r="J3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>17</v>
       </c>
-      <c r="I2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J2" t="s">
-        <v>17</v>
+      <c r="B4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4">
+        <v>123456</v>
+      </c>
+      <c r="D4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F4" t="s">
+        <v>19</v>
+      </c>
+      <c r="G4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H4" t="s">
+        <v>35</v>
+      </c>
+      <c r="I4" t="s">
+        <v>36</v>
+      </c>
+      <c r="J4" t="s">
+        <v>37</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C3" t="s">
-        <v>12</v>
-      </c>
-      <c r="D3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E3" t="s">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
         <v>21</v>
       </c>
-      <c r="F3" t="s">
+      <c r="B5" t="s">
         <v>22</v>
       </c>
-      <c r="G3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H3" t="s">
-        <v>24</v>
-      </c>
-      <c r="I3" t="s">
-        <v>17</v>
-      </c>
-      <c r="J3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A4" t="s">
-        <v>25</v>
-      </c>
-      <c r="B4" t="s">
-        <v>26</v>
-      </c>
-      <c r="C4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D4" t="s">
-        <v>13</v>
-      </c>
-      <c r="E4" t="s">
-        <v>14</v>
-      </c>
-      <c r="F4" t="s">
-        <v>27</v>
-      </c>
-      <c r="G4" t="s">
-        <v>28</v>
-      </c>
-      <c r="H4" t="s">
-        <v>17</v>
-      </c>
-      <c r="I4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A5" t="s">
+      <c r="C5">
+        <v>123456</v>
+      </c>
+      <c r="D5" t="s">
         <v>29</v>
-      </c>
-      <c r="B5" t="s">
-        <v>30</v>
-      </c>
-      <c r="C5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D5" t="s">
-        <v>13</v>
       </c>
       <c r="E5" t="s">
         <v>31</v>
       </c>
       <c r="F5" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="G5" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="H5" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="I5" t="s">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="J5" t="s">
-        <v>17</v>
+        <v>37</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="B6" t="s">
-        <v>35</v>
-      </c>
-      <c r="C6" t="s">
-        <v>12</v>
+        <v>26</v>
+      </c>
+      <c r="C6">
+        <v>123456</v>
       </c>
       <c r="D6" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="E6" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="F6" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="G6" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="H6" t="s">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="I6" t="s">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="J6" t="s">
-        <v>17</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
+  <dataValidations count="4">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="只能填写 0、1、2" sqref="D75069:D1048576" xr:uid="{6F40360A-3C8C-4535-AD54-40EB5AC7F4F1}">
+      <formula1>"0,1,2"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="只能填写未知,男,女" sqref="D2:D6" xr:uid="{22B40D24-6688-4ED5-8865-4AAD2996B668}">
+      <formula1>"未知,男,女"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="只能输入未知,男,女" sqref="D7:D75068" xr:uid="{5C678B53-7613-4583-9375-42AD64729B80}">
+      <formula1>"未知,男,女"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="只能输入student,teacher,admin" sqref="E2:E76076" xr:uid="{E71F3E65-0334-4D19-9AEC-00157EB24FB1}">
+      <formula1>"student,teacher,admin"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
